--- a/obuv_07_07_2026_fin.xlsx
+++ b/obuv_07_07_2026_fin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Monastyrska\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DB75EC-9847-4DF1-BFED-2EB11972ACB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8407AFC-FE13-4E4D-80D6-7B4E08A29A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="-840" windowWidth="29145" windowHeight="15465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26040" yWindow="1410" windowWidth="19425" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="176">
   <si>
     <t>Артикул</t>
   </si>
@@ -442,6 +442,116 @@
   </si>
   <si>
     <t>Аргентина</t>
+  </si>
+  <si>
+    <t>0000000000580</t>
+  </si>
+  <si>
+    <t>10A</t>
+  </si>
+  <si>
+    <t>0000000000578</t>
+  </si>
+  <si>
+    <t>04H</t>
+  </si>
+  <si>
+    <t>3copy_Soursedemoproduct</t>
+  </si>
+  <si>
+    <t>mp894900</t>
+  </si>
+  <si>
+    <t>0000000000575</t>
+  </si>
+  <si>
+    <t>https://aniart-partner.intertop.com/images/products/894900/roDy5QceV0Va4OyQZcGPiwKPM1mnltv8NoExMLvy.jpeg
+https://aniart-partner.intertop.com/images/products/894900/gP9TVB3SofG5jLtAxv4lsfqPYZjiIdDxa635sc3v.jpeg</t>
+  </si>
+  <si>
+    <t>DEMO 3 Data source Кросівки Duramo Speed</t>
+  </si>
+  <si>
+    <t>1Кроссовки Duramo Speed</t>
+  </si>
+  <si>
+    <t>Характеристики Амортизація Lightstrike Сітчастий верх Стабільне і сприйнятливе відчуття Стандартний крій Текстильна підкладка Шнурівка Підошва Adiwear Верх цієї моделі на 50% складається із перероблених волокон Перепад підошви: 6,5 мм (п'ятка: 35 мм / носок: 28,5 мм) Вага: 238 г (розмір 37) Опис Поєднання легкого і повітропроникного верху з сітки з повнорозмірною проміжною підошвою LIGHTSTRIKE для більшої швидкості було створене для бігунів, які бажають вийти на новий рівень. Модель виготовлена з перероблених матеріалів і представляє одне з наших рішень щодо скорочення пластикових відходів.</t>
+  </si>
+  <si>
+    <t>wewewewe</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Туфлі та лофери</t>
+  </si>
+  <si>
+    <t>Броги</t>
+  </si>
+  <si>
+    <t>adidas</t>
+  </si>
+  <si>
+    <t>Женское</t>
+  </si>
+  <si>
+    <t>Комбінований верх</t>
+  </si>
+  <si>
+    <t>Весна-Літо</t>
+  </si>
+  <si>
+    <t>Sport</t>
+  </si>
+  <si>
+    <t>Індонезія</t>
+  </si>
+  <si>
+    <t>Duramo</t>
+  </si>
+  <si>
+    <t>Поліуретан</t>
+  </si>
+  <si>
+    <t>0000000000576</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>2_0copy_Soursedelete1-Qatests</t>
+  </si>
+  <si>
+    <t>2_0copy_Soursedelete1-Qatest1ss</t>
+  </si>
+  <si>
+    <t>mp894843</t>
+  </si>
+  <si>
+    <t>366.00</t>
+  </si>
+  <si>
+    <t>https://aniart-partner.intertop.com/images/products/894843/XcGKlOQ4wIHQZXUp7u9fdCWjUl1lD6hTXcEg2rA9.jpeg
+https://aniart-partner.intertop.com/images/products/894843/B3EVlaScijR6VpWCSeqbSjZhLM0nrHmIUbBUob0X.jpeg</t>
+  </si>
+  <si>
+    <t>Data source 2.0 Кросівки Duramo Speed</t>
+  </si>
+  <si>
+    <t>Кроссовки Duramo Speed</t>
+  </si>
+  <si>
+    <t>Характеристики Амортизация Lightstrike Сетчатый верх Стабильное и отзывчивое ощущение Стандартный крой Текстильная подкладка Шнуровка Подошва Adiwear Верх этой модели на 50% состоит из переработанных волокон Перепад подошвы: 6,5 мм (пятка: 35 мм / носок: 28,5 мм) Вес: 238 г (размер 37) Описание Сочетание легкого и воздухопроницаемого верха из сетки с полноразмерной промежуточной подошвой LIGHTSTRIKE, для большей скорости, и прочной подошвой было создано для бегунов, желающих выйти на новый уровень. Модель изготовлена из переработанных материалов и представляет одно из наших решений по сокращению пластиковых отходов.</t>
+  </si>
+  <si>
+    <t>xlsx</t>
+  </si>
+  <si>
+    <t>2_0copy_Soursedelete1-Qatests_2</t>
+  </si>
+  <si>
+    <t>222.00</t>
   </si>
 </sst>
 </file>
@@ -822,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.7265625" style="1" customWidth="1"/>
@@ -1206,7 +1316,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="1">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>108</v>
@@ -1265,61 +1375,58 @@
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
       </c>
       <c r="F4" s="1">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>113</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>118</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="W4" s="1" t="s">
         <v>120</v>
@@ -1334,10 +1441,526 @@
         <v>123</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="AI4" s="1" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>45</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AI5" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>45</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AI6" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>45</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>45</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AI8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ8" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>45</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AB9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AG9" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>45</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/obuv_07_07_2026_fin.xlsx
+++ b/obuv_07_07_2026_fin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Monastyrska\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8407AFC-FE13-4E4D-80D6-7B4E08A29A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D827A87A-C58E-4223-AF1E-83F8BA67D234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26040" yWindow="1410" windowWidth="19425" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="10" windowWidth="19430" windowHeight="10310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1669,7 +1669,7 @@
         <v>156</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="AB7" s="1" t="s">
         <v>123</v>
@@ -1761,7 +1761,7 @@
         <v>156</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="AB8" s="1" t="s">
         <v>123</v>

--- a/obuv_07_07_2026_fin.xlsx
+++ b/obuv_07_07_2026_fin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Monastyrska\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E34479F-2978-40F0-A972-37B6B8BC7A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2660F383-423D-4A98-B1B0-26FDA9E7BA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23895" yWindow="945" windowWidth="19425" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1282,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="1">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>108</v>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="1">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>108</v>
@@ -1430,7 +1430,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="1">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>108</v>
@@ -1507,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>108</v>
@@ -1584,7 +1584,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>108</v>
@@ -1676,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>108</v>
